--- a/Team-Data/2014-15/3-14-2014-15.xlsx
+++ b/Team-Data/2014-15/3-14-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,10 +806,10 @@
         <v>6.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
@@ -757,7 +824,7 @@
         <v>12</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK2" t="n">
         <v>3</v>
@@ -772,7 +839,7 @@
         <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP2" t="n">
         <v>23</v>
@@ -808,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB2" t="n">
         <v>9</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" t="n">
         <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>0.446</v>
+        <v>0.438</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -861,7 +928,7 @@
         <v>38.8</v>
       </c>
       <c r="J3" t="n">
-        <v>88.2</v>
+        <v>88.3</v>
       </c>
       <c r="K3" t="n">
         <v>0.44</v>
@@ -894,10 +961,10 @@
         <v>43.9</v>
       </c>
       <c r="U3" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="V3" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W3" t="n">
         <v>8</v>
@@ -912,25 +979,25 @@
         <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.6</v>
+        <v>100.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF3" t="n">
         <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH3" t="n">
         <v>11</v>
@@ -951,7 +1018,7 @@
         <v>12</v>
       </c>
       <c r="AN3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
@@ -963,10 +1030,10 @@
         <v>18</v>
       </c>
       <c r="AR3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS3" t="n">
         <v>12</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -975,16 +1042,16 @@
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -1025,52 +1092,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
         <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>0.406</v>
+        <v>0.397</v>
       </c>
       <c r="H4" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I4" t="n">
         <v>36.6</v>
       </c>
       <c r="J4" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L4" t="n">
         <v>6.6</v>
       </c>
       <c r="M4" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.325</v>
+        <v>0.327</v>
       </c>
       <c r="O4" t="n">
         <v>16.4</v>
       </c>
       <c r="P4" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.741</v>
+        <v>0.742</v>
       </c>
       <c r="R4" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S4" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T4" t="n">
         <v>42.2</v>
@@ -1082,28 +1149,28 @@
         <v>14.4</v>
       </c>
       <c r="W4" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.2</v>
+        <v>96.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.6</v>
+        <v>-3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
@@ -1115,13 +1182,13 @@
         <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
         <v>21</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1133,7 +1200,7 @@
         <v>20</v>
       </c>
       <c r="AN4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO4" t="n">
         <v>21</v>
@@ -1148,10 +1215,10 @@
         <v>23</v>
       </c>
       <c r="AS4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU4" t="n">
         <v>27</v>
@@ -1169,10 +1236,10 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB4" t="n">
         <v>24</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -1285,19 +1352,19 @@
         <v>-1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
         <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
@@ -1306,7 +1373,7 @@
         <v>10</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL5" t="n">
         <v>27</v>
@@ -1324,7 +1391,7 @@
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR5" t="n">
         <v>25</v>
@@ -1348,7 +1415,7 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1552,7 @@
         <v>23</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK6" t="n">
         <v>21</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1509,7 +1576,7 @@
         <v>2</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
         <v>6</v>
@@ -1527,10 +1594,10 @@
         <v>29</v>
       </c>
       <c r="AX6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
         <v>2</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -1652,22 +1719,22 @@
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
         <v>10</v>
@@ -1685,16 +1752,16 @@
         <v>5</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
         <v>17</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
         <v>17</v>
@@ -1703,16 +1770,16 @@
         <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
       </c>
       <c r="AY7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ7" t="n">
         <v>5</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E8" t="n">
         <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>0.636</v>
+        <v>0.627</v>
       </c>
       <c r="H8" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I8" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
         <v>0.461</v>
@@ -1792,19 +1859,19 @@
         <v>21.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R8" t="n">
         <v>10.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V8" t="n">
         <v>12.7</v>
@@ -1825,25 +1892,25 @@
         <v>21.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.7</v>
+        <v>104.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1867,19 +1934,19 @@
         <v>20</v>
       </c>
       <c r="AP8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ8" t="n">
         <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT8" t="n">
         <v>23</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>21</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1891,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>-3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF9" t="n">
         <v>23</v>
@@ -2025,7 +2092,7 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
         <v>17</v>
@@ -2043,13 +2110,13 @@
         <v>13</v>
       </c>
       <c r="AN9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO9" t="n">
         <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
         <v>24</v>
@@ -2058,7 +2125,7 @@
         <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
         <v>6</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>0.348</v>
+        <v>0.354</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J10" t="n">
         <v>86.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.426</v>
+        <v>0.427</v>
       </c>
       <c r="L10" t="n">
         <v>8.300000000000001</v>
@@ -2153,16 +2220,16 @@
         <v>16.2</v>
       </c>
       <c r="P10" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.707</v>
+        <v>0.709</v>
       </c>
       <c r="R10" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S10" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T10" t="n">
         <v>45.3</v>
@@ -2183,19 +2250,19 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>97.90000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC10" t="n">
         <v>-2</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,25 +2274,25 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
         <v>20</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM10" t="n">
         <v>11</v>
       </c>
       <c r="AN10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO10" t="n">
         <v>23</v>
@@ -2255,7 +2322,7 @@
         <v>16</v>
       </c>
       <c r="AX10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
@@ -2264,7 +2331,7 @@
         <v>8</v>
       </c>
       <c r="BA10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8</v>
+        <v>0.797</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
@@ -2317,43 +2384,43 @@
         <v>41.4</v>
       </c>
       <c r="J11" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="K11" t="n">
         <v>0.477</v>
       </c>
       <c r="L11" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="M11" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.395</v>
+        <v>0.391</v>
       </c>
       <c r="O11" t="n">
         <v>16.1</v>
       </c>
       <c r="P11" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="R11" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S11" t="n">
         <v>34.4</v>
       </c>
       <c r="T11" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U11" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="V11" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W11" t="n">
         <v>9.4</v>
@@ -2362,22 +2429,22 @@
         <v>6.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB11" t="n">
-        <v>109.7</v>
+        <v>109.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2389,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
@@ -2410,13 +2477,13 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP11" t="n">
         <v>25</v>
       </c>
-      <c r="AP11" t="n">
-        <v>26</v>
-      </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
@@ -2425,7 +2492,7 @@
         <v>4</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -2481,55 +2548,55 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
         <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.656</v>
+        <v>0.662</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>84.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
       </c>
       <c r="L12" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="M12" t="n">
         <v>33.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.719</v>
+        <v>0.717</v>
       </c>
       <c r="R12" t="n">
         <v>12</v>
       </c>
       <c r="S12" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U12" t="n">
         <v>22</v>
@@ -2547,22 +2614,22 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB12" t="n">
         <v>103</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
@@ -2571,7 +2638,7 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>19</v>
@@ -2589,22 +2656,22 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
         <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT12" t="n">
         <v>14</v>
@@ -2616,16 +2683,16 @@
         <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
         <v>13</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -2663,22 +2730,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" t="n">
         <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>0.462</v>
+        <v>0.469</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J13" t="n">
         <v>83.2</v>
@@ -2687,10 +2754,10 @@
         <v>0.438</v>
       </c>
       <c r="L13" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M13" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N13" t="n">
         <v>0.341</v>
@@ -2699,10 +2766,10 @@
         <v>16.6</v>
       </c>
       <c r="P13" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R13" t="n">
         <v>10.5</v>
@@ -2717,10 +2784,10 @@
         <v>21.5</v>
       </c>
       <c r="V13" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W13" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="X13" t="n">
         <v>4.5</v>
@@ -2729,19 +2796,19 @@
         <v>4.9</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA13" t="n">
         <v>21.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>96.5</v>
+        <v>96.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AE13" t="n">
         <v>17</v>
@@ -2753,13 +2820,13 @@
         <v>17</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK13" t="n">
         <v>23</v>
@@ -2768,7 +2835,7 @@
         <v>18</v>
       </c>
       <c r="AM13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN13" t="n">
         <v>19</v>
@@ -2777,10 +2844,10 @@
         <v>19</v>
       </c>
       <c r="AP13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
         <v>20</v>
@@ -2801,7 +2868,7 @@
         <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY13" t="n">
         <v>17</v>
@@ -2810,7 +2877,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
         <v>23</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2968,10 +3035,10 @@
         <v>27</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>0.27</v>
+        <v>0.266</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J15" t="n">
-        <v>86.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
         <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N15" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="O15" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P15" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T15" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="U15" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
         <v>12.9</v>
@@ -3090,22 +3157,22 @@
         <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,10 +3187,10 @@
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
@@ -3144,16 +3211,16 @@
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS15" t="n">
         <v>13</v>
       </c>
       <c r="AT15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU15" t="n">
         <v>20</v>
@@ -3165,16 +3232,16 @@
         <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB15" t="n">
         <v>17</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F16" t="n">
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>0.697</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
@@ -3233,61 +3300,61 @@
         <v>0.458</v>
       </c>
       <c r="L16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
         <v>15.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.334</v>
+        <v>0.331</v>
       </c>
       <c r="O16" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P16" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R16" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S16" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T16" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U16" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V16" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="W16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>4.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB16" t="n">
         <v>99</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3305,7 +3372,7 @@
         <v>13</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK16" t="n">
         <v>8</v>
@@ -3317,7 +3384,7 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AO16" t="n">
         <v>7</v>
@@ -3338,7 +3405,7 @@
         <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV16" t="n">
         <v>6</v>
@@ -3347,13 +3414,13 @@
         <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY16" t="n">
         <v>23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA16" t="n">
         <v>14</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AE17" t="n">
         <v>18</v>
@@ -3493,7 +3560,7 @@
         <v>11</v>
       </c>
       <c r="AL17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AM17" t="n">
         <v>19</v>
@@ -3505,10 +3572,10 @@
         <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV17" t="n">
         <v>21</v>
@@ -3535,7 +3602,7 @@
         <v>6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
         <v>8</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" t="n">
         <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G18" t="n">
-        <v>0.515</v>
+        <v>0.523</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J18" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K18" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L18" t="n">
         <v>6.9</v>
@@ -3603,28 +3670,28 @@
         <v>18.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.37</v>
+        <v>0.372</v>
       </c>
       <c r="O18" t="n">
         <v>16.1</v>
       </c>
       <c r="P18" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.769</v>
+        <v>0.771</v>
       </c>
       <c r="R18" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S18" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T18" t="n">
         <v>41.5</v>
       </c>
       <c r="U18" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V18" t="n">
         <v>16.8</v>
@@ -3645,13 +3712,13 @@
         <v>20</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
@@ -3666,10 +3733,10 @@
         <v>10</v>
       </c>
       <c r="AI18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK18" t="n">
         <v>6</v>
@@ -3684,13 +3751,13 @@
         <v>3</v>
       </c>
       <c r="AO18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AR18" t="n">
         <v>24</v>
@@ -3708,22 +3775,22 @@
         <v>29</v>
       </c>
       <c r="AW18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY18" t="n">
         <v>13</v>
       </c>
-      <c r="AY18" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA18" t="n">
         <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC18" t="n">
         <v>14</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-7.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3863,7 +3930,7 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3884,7 +3951,7 @@
         <v>24</v>
       </c>
       <c r="AU19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV19" t="n">
         <v>22</v>
@@ -3905,7 +3972,7 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20" t="n">
         <v>29</v>
       </c>
       <c r="G20" t="n">
-        <v>0.547</v>
+        <v>0.554</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J20" t="n">
-        <v>82.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
@@ -3967,37 +4034,37 @@
         <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="O20" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P20" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.772</v>
+        <v>0.766</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
         <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="U20" t="n">
         <v>21.8</v>
       </c>
       <c r="V20" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W20" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,37 +4073,37 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
         <v>99.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI20" t="n">
         <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
@@ -4045,25 +4112,25 @@
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
         <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -4119,58 +4186,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E21" t="n">
         <v>13</v>
       </c>
       <c r="F21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2</v>
+        <v>0.203</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J21" t="n">
-        <v>82.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.43</v>
+        <v>0.431</v>
       </c>
       <c r="L21" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N21" t="n">
         <v>0.349</v>
       </c>
       <c r="O21" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="P21" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.766</v>
+        <v>0.769</v>
       </c>
       <c r="R21" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S21" t="n">
         <v>29.6</v>
       </c>
       <c r="T21" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U21" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V21" t="n">
         <v>14.3</v>
@@ -4185,7 +4252,7 @@
         <v>4.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA21" t="n">
         <v>19.2</v>
@@ -4194,10 +4261,10 @@
         <v>92.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-9</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4209,19 +4276,19 @@
         <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
         <v>28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK21" t="n">
         <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>30</v>
@@ -4251,22 +4318,22 @@
         <v>18</v>
       </c>
       <c r="AV21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
         <v>23</v>
       </c>
       <c r="AX21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ21" t="n">
         <v>27</v>
       </c>
       <c r="BA21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
@@ -4391,7 +4458,7 @@
         <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4409,7 +4476,7 @@
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO22" t="n">
         <v>6</v>
@@ -4418,7 +4485,7 @@
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4439,13 +4506,13 @@
         <v>22</v>
       </c>
       <c r="AX22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA22" t="n">
         <v>18</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E23" t="n">
         <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G23" t="n">
-        <v>0.318</v>
+        <v>0.313</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4501,37 +4568,37 @@
         <v>37.3</v>
       </c>
       <c r="J23" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
         <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
         <v>0.354</v>
       </c>
       <c r="O23" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="P23" t="n">
         <v>19.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.726</v>
+        <v>0.727</v>
       </c>
       <c r="R23" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="U23" t="n">
         <v>20.4</v>
@@ -4543,10 +4610,10 @@
         <v>7.8</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>21.1</v>
@@ -4555,13 +4622,13 @@
         <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.6</v>
+        <v>-5.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4576,10 +4643,10 @@
         <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK23" t="n">
         <v>13</v>
@@ -4606,7 +4673,7 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT23" t="n">
         <v>27</v>
@@ -4621,13 +4688,13 @@
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -4665,43 +4732,43 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G24" t="n">
-        <v>0.227</v>
+        <v>0.231</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="J24" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.408</v>
+        <v>0.409</v>
       </c>
       <c r="L24" t="n">
         <v>8</v>
       </c>
       <c r="M24" t="n">
-        <v>25.5</v>
+        <v>25.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.316</v>
+        <v>0.318</v>
       </c>
       <c r="O24" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P24" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q24" t="n">
         <v>0.676</v>
@@ -4710,16 +4777,16 @@
         <v>11.7</v>
       </c>
       <c r="S24" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T24" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U24" t="n">
         <v>20.6</v>
       </c>
       <c r="V24" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="W24" t="n">
         <v>9.800000000000001</v>
@@ -4734,7 +4801,7 @@
         <v>21.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB24" t="n">
         <v>91</v>
@@ -4743,13 +4810,13 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
       </c>
       <c r="AF24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG24" t="n">
         <v>28</v>
@@ -4770,10 +4837,10 @@
         <v>13</v>
       </c>
       <c r="AM24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO24" t="n">
         <v>22</v>
@@ -4785,7 +4852,7 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4803,13 +4870,13 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA24" t="n">
         <v>15</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -4958,13 +5025,13 @@
         <v>13</v>
       </c>
       <c r="AO25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP25" t="n">
         <v>20</v>
       </c>
       <c r="AQ25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR25" t="n">
         <v>14</v>
@@ -4991,13 +5058,13 @@
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA25" t="n">
         <v>12</v>
       </c>
       <c r="BB25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>5.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE26" t="n">
         <v>4</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>26</v>
@@ -5149,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5167,7 +5234,7 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5176,7 +5243,7 @@
         <v>3</v>
       </c>
       <c r="BA26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB26" t="n">
         <v>8</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E27" t="n">
         <v>22</v>
       </c>
       <c r="F27" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G27" t="n">
-        <v>0.338</v>
+        <v>0.344</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
@@ -5256,10 +5323,10 @@
         <v>11.1</v>
       </c>
       <c r="S27" t="n">
-        <v>33.4</v>
+        <v>33.6</v>
       </c>
       <c r="T27" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U27" t="n">
         <v>19.8</v>
@@ -5283,13 +5350,13 @@
         <v>24.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.9</v>
+        <v>101</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.4</v>
+        <v>-4.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,7 +5368,7 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5334,10 +5401,10 @@
         <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E28" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F28" t="n">
         <v>24</v>
       </c>
       <c r="G28" t="n">
-        <v>0.619</v>
+        <v>0.625</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
@@ -5411,52 +5478,52 @@
         <v>38.4</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.362</v>
+        <v>0.364</v>
       </c>
       <c r="O28" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P28" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R28" t="n">
         <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U28" t="n">
         <v>24</v>
       </c>
       <c r="V28" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W28" t="n">
         <v>7.8</v>
       </c>
       <c r="X28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z28" t="n">
         <v>19.5</v>
@@ -5471,10 +5538,10 @@
         <v>4.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
         <v>6</v>
@@ -5492,22 +5559,22 @@
         <v>14</v>
       </c>
       <c r="AK28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AP28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ28" t="n">
         <v>9</v>
@@ -5516,10 +5583,10 @@
         <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF29" t="n">
         <v>10</v>
@@ -5665,7 +5732,7 @@
         <v>10</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI29" t="n">
         <v>10</v>
@@ -5680,7 +5747,7 @@
         <v>9</v>
       </c>
       <c r="AM29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN29" t="n">
         <v>15</v>
@@ -5716,7 +5783,7 @@
         <v>19</v>
       </c>
       <c r="AY29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ29" t="n">
         <v>21</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F30" t="n">
         <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>0.446</v>
+        <v>0.438</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
@@ -5775,7 +5842,7 @@
         <v>35.6</v>
       </c>
       <c r="J30" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="K30" t="n">
         <v>0.45</v>
@@ -5784,10 +5851,10 @@
         <v>7.2</v>
       </c>
       <c r="M30" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="N30" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O30" t="n">
         <v>16.8</v>
@@ -5796,7 +5863,7 @@
         <v>23</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="R30" t="n">
         <v>11.9</v>
@@ -5829,22 +5896,22 @@
         <v>19.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>95.09999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AE30" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF30" t="n">
         <v>19</v>
       </c>
       <c r="AG30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH30" t="n">
         <v>30</v>
@@ -5862,13 +5929,13 @@
         <v>17</v>
       </c>
       <c r="AM30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP30" t="n">
         <v>15</v>
@@ -5880,7 +5947,7 @@
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT30" t="n">
         <v>13</v>
@@ -5895,10 +5962,10 @@
         <v>21</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ30" t="n">
         <v>7</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
@@ -5939,37 +6006,37 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F31" t="n">
         <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>0.576</v>
+        <v>0.569</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J31" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.467</v>
+        <v>0.466</v>
       </c>
       <c r="L31" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M31" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.359</v>
+        <v>0.355</v>
       </c>
       <c r="O31" t="n">
         <v>15.8</v>
@@ -5978,10 +6045,10 @@
         <v>21.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R31" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S31" t="n">
         <v>33.6</v>
@@ -6005,19 +6072,19 @@
         <v>4.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA31" t="n">
         <v>19.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.7</v>
+        <v>98.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6029,13 +6096,13 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
       </c>
       <c r="AJ31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK31" t="n">
         <v>4</v>
@@ -6047,7 +6114,7 @@
         <v>27</v>
       </c>
       <c r="AN31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO31" t="n">
         <v>27</v>
@@ -6062,10 +6129,10 @@
         <v>18</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU31" t="n">
         <v>5</v>
@@ -6074,16 +6141,16 @@
         <v>24</v>
       </c>
       <c r="AW31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX31" t="n">
         <v>17</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-14-2014-15</t>
+          <t>2015-03-14</t>
         </is>
       </c>
     </row>
